--- a/artfynd/A 26009-2024 artfynd.xlsx
+++ b/artfynd/A 26009-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2307855</v>
+        <v>6769735</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522219.1351885367</v>
+        <v>522242</v>
       </c>
       <c r="R2" t="n">
-        <v>6951116.937054338</v>
+        <v>6951333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,21 +757,11 @@
           <t>2008-06-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-06-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,11 +770,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig kalbarrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -806,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119625544</v>
+        <v>73098711</v>
       </c>
       <c r="B3" t="n">
-        <v>90334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,34 +797,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Drolvägen, Jmt</t>
+          <t>Bensjön / SV /, Tunadal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522267</v>
+        <v>522254</v>
       </c>
       <c r="R3" t="n">
-        <v>6951136</v>
+        <v>6951341</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,14 +863,24 @@
           <t>Bräcke</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Z-Brä-1457</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2008-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2008-06-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10 plantor. Drolvägen. Koordinat O1481028, N6953466 (±10m) RT90 2.5 gon. Kopia till floraväkteriet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,65 +895,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124547062</v>
+        <v>119625544</v>
       </c>
       <c r="B4" t="n">
-        <v>57433</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102110</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bensjön, Jmt</t>
+          <t>Drolvägen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522175</v>
+        <v>522267</v>
       </c>
       <c r="R4" t="n">
-        <v>6951079</v>
+        <v>6951136</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,19 +996,358 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127830705</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bensjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522175</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6951079</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Britta Sterner</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Britta Sterner, Agnes  Blomgren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2307855</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Drolvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>522219</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6951117</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2008-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2008-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>fuktig kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5169805</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Drolvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522174</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6951339</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2008-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2008-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>fuktig kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26009-2024 artfynd.xlsx
+++ b/artfynd/A 26009-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6769735</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73098711</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625544</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830705</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2307855</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,8 +1378,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5169805</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>